--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_72_R8.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_72_R8.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1551</v>
+        <v>5.8922</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1273</v>
+        <v>3.003</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0278</v>
+        <v>2.8892</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6724</v>
+        <v>2.7895</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9471000000000001</v>
+        <v>1.6218</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6195</v>
+        <v>1.1677</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6798</v>
+        <v>2.2176</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6820000000000001</v>
+        <v>1.3612</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3618</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0073</v>
+        <v>0.5719</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2651</v>
+        <v>0.2606</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2578</v>
+        <v>0.3113</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2473</v>
+        <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2507</v>
+        <v>-0.521</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4629</v>
+        <v>-0.2869</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2122</v>
+        <v>-0.2341</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7235</v>
+        <v>5.6229</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7671</v>
+        <v>2.4942</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9564</v>
+        <v>3.1286</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7895</v>
+        <v>0.6724</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6218</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1677</v>
+        <v>1.6195</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2176</v>
+        <v>0.6798</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3612</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8564000000000001</v>
+        <v>1.3618</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5719</v>
+        <v>-0.0073</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2606</v>
+        <v>-0.2651</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3113</v>
+        <v>0.2578</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5515</v>
+        <v>3.2473</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6897</v>
+        <v>0.7185</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5228</v>
+        <v>0.8298</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1669</v>
+        <v>-0.1114</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0707</v>
+        <v>4.1454</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6944</v>
+        <v>1.769</v>
       </c>
       <c r="F4" t="n">
         <v>2.3763</v>
@@ -766,10 +766,10 @@
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0668</v>
+        <v>0.1415</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2513</v>
+        <v>-0.1766</v>
       </c>
       <c r="U4" t="n">
         <v>0.3181</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>S. JOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.522</v>
+        <v>3.8715</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2834</v>
+        <v>1.6254</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2386</v>
+        <v>2.2461</v>
       </c>
       <c r="G5" t="n">
-        <v>0.385</v>
+        <v>3.5521</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5822</v>
+        <v>-0.5869</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9672</v>
+        <v>4.139</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9392</v>
+        <v>3.2449</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.981</v>
+        <v>-0.1646</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9203</v>
+        <v>3.4094</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5542</v>
+        <v>0.3072</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6012</v>
+        <v>-0.4223</v>
       </c>
       <c r="O5" t="n">
-        <v>0.047</v>
+        <v>0.7296</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0075</v>
+        <v>-0.3765</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1766</v>
+        <v>-0.4597</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1691</v>
+        <v>0.0833</v>
       </c>
       <c r="V5" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. JOVIC</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.006</v>
+        <v>3.6975</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1968</v>
+        <v>2.3581</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8092</v>
+        <v>1.3394</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5521</v>
+        <v>0.385</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5869</v>
+        <v>-1.5822</v>
       </c>
       <c r="I6" t="n">
-        <v>4.139</v>
+        <v>1.9672</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2449</v>
+        <v>0.9392</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1646</v>
+        <v>-0.981</v>
       </c>
       <c r="L6" t="n">
-        <v>3.4094</v>
+        <v>1.9203</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3072</v>
+        <v>-0.5542</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4223</v>
+        <v>-0.6012</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7296</v>
+        <v>0.047</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2419</v>
+        <v>0.168</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8883</v>
+        <v>-0.1019</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3536</v>
+        <v>0.27</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VOIGTMANN</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6683</v>
+        <v>1.1227</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7227</v>
+        <v>-0.763</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0544</v>
+        <v>1.8857</v>
       </c>
       <c r="G7" t="n">
-        <v>1.076</v>
+        <v>-1.9139</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4201</v>
+        <v>-3.6974</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6558</v>
+        <v>1.7835</v>
       </c>
       <c r="J7" t="n">
-        <v>1.312</v>
+        <v>-0.9522</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8101</v>
+        <v>-2.7925</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5018</v>
+        <v>1.8402</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.236</v>
+        <v>-0.9617</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.39</v>
+        <v>-0.9049</v>
       </c>
       <c r="O7" t="n">
-        <v>0.154</v>
+        <v>-0.0568</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4352</v>
+        <v>0.4826</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1968</v>
+        <v>0.0474</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2384</v>
+        <v>0.4351</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.0026</v>
+        <v>0.9304</v>
       </c>
       <c r="W7" t="n">
-        <v>1.214</v>
+        <v>0.1418</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.2166</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>J. VOIGTMANN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2161</v>
+        <v>0.6999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8377</v>
+        <v>2.3256</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0537</v>
+        <v>-1.6258</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9139</v>
+        <v>1.076</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.6974</v>
+        <v>0.4201</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7835</v>
+        <v>0.6558</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9522</v>
+        <v>1.312</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.7925</v>
+        <v>0.8101</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8402</v>
+        <v>0.5018</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9617</v>
+        <v>-0.236</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9049</v>
+        <v>-0.39</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0568</v>
+        <v>0.154</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5759</v>
+        <v>0.4668</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0272</v>
+        <v>-0.2003</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6032</v>
+        <v>0.6671</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9304</v>
+        <v>-2.0026</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1418</v>
+        <v>1.214</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7886</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4214</v>
+        <v>0.1257</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0184</v>
+        <v>-2.1796</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4398</v>
+        <v>2.3054</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6383</v>
@@ -1156,13 +1156,13 @@
         <v>2.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5236</v>
+        <v>0.228</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3383</v>
+        <v>0.177</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1854</v>
+        <v>0.051</v>
       </c>
       <c r="V9" t="n">
         <v>1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>S. DINWIDDIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1939</v>
+        <v>-1.4613</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2363</v>
+        <v>-2.885</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0423</v>
+        <v>1.4236</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3168</v>
+        <v>-3.3345</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6915</v>
+        <v>-0.8751</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3747</v>
+        <v>-2.4594</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2139</v>
+        <v>-2.3944</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5881999999999999</v>
+        <v>-0.4636</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6257</v>
+        <v>-1.9308</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.897</v>
+        <v>-0.9401</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1034</v>
+        <v>-0.4116</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0004</v>
+        <v>-0.5286</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5515</v>
+        <v>3.0154</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1129</v>
+        <v>-0.1474</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1889</v>
+        <v>0.0788</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.076</v>
+        <v>-0.2262</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5361</v>
+        <v>1.3247</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>-0.4254</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. DINWIDDIE</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6977</v>
+        <v>-2.3215</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7853</v>
+        <v>-3.3975</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0876</v>
+        <v>1.0759</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3345</v>
+        <v>0.3168</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8751</v>
+        <v>0.6915</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4594</v>
+        <v>-0.3747</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3944</v>
+        <v>1.2139</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4636</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9308</v>
+        <v>0.6257</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9401</v>
+        <v>-0.897</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4116</v>
+        <v>0.1034</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5286</v>
+        <v>-1.0004</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6959</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>-4.639</v>
       </c>
       <c r="R11" t="n">
-        <v>3.0154</v>
+        <v>2.5515</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3838</v>
+        <v>-0.0147</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8215</v>
+        <v>0.0277</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5623</v>
+        <v>-0.0424</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3247</v>
+        <v>-0.5361</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.4254</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1779</v>
+        <v>-2.9345</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9029</v>
+        <v>-2.5923</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.275</v>
+        <v>-0.3422</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9087</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1046</v>
+        <v>0.3479</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.224</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3286</v>
+        <v>0.2614</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6778999999999999</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.7136</v>
+        <v>18.4605</v>
       </c>
       <c r="E13" t="n">
-        <v>1.011099999999999</v>
+        <v>1.7579</v>
       </c>
       <c r="F13" t="n">
-        <v>16.7023</v>
+        <v>16.7022</v>
       </c>
       <c r="G13" t="n">
-        <v>3.946099999999999</v>
+        <v>3.946099999999998</v>
       </c>
       <c r="H13" t="n">
         <v>-3.415</v>
@@ -1441,7 +1441,7 @@
         <v>7.360899999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>7.843200000000001</v>
+        <v>7.843200000000003</v>
       </c>
       <c r="K13" t="n">
         <v>-0.08560000000000038</v>
@@ -1450,10 +1450,10 @@
         <v>7.928700000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.897000000000001</v>
+        <v>-3.897</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.329299999999999</v>
+        <v>-3.3293</v>
       </c>
       <c r="O13" t="n">
         <v>-0.5675999999999998</v>
@@ -1468,13 +1468,13 @@
         <v>23.1953</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7467999999999999</v>
+        <v>1.4937</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7248</v>
+        <v>0.02179999999999992</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4718</v>
+        <v>1.4719</v>
       </c>
       <c r="V13" t="n">
         <v>7.2218</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4337</v>
+        <v>3.9581</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0938</v>
+        <v>2.0322</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3399</v>
+        <v>1.9258</v>
       </c>
       <c r="G14" t="n">
         <v>2.1267</v>
@@ -1546,13 +1546,13 @@
         <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4693</v>
+        <v>0.9937</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4787</v>
+        <v>0.4171</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9906</v>
+        <v>0.5766</v>
       </c>
       <c r="V14" t="n">
         <v>0.1418</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5032</v>
+        <v>3.5191</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2645</v>
+        <v>2.8543</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2386</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>0.6894</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8821</v>
+        <v>0.1338</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8804</v>
+        <v>-0.2906</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0018</v>
+        <v>0.4244</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1266</v>
+        <v>1.2782</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0909</v>
+        <v>2.1245</v>
       </c>
       <c r="G16" t="n">
         <v>0.6641</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9291</v>
+        <v>-0.7776</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6304</v>
+        <v>-0.5968</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8979</v>
+        <v>0.5269</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6311</v>
+        <v>1.1593</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7332</v>
+        <v>-0.6324</v>
       </c>
       <c r="G17" t="n">
         <v>0.3431</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5548</v>
+        <v>0.1838</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4876</v>
+        <v>0.0158</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3654</v>
+        <v>-0.6919</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0824</v>
+        <v>-0.6106</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.283</v>
+        <v>-0.0813</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5026</v>
@@ -1858,13 +1858,13 @@
         <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8602</v>
+        <v>-0.1867</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5975</v>
+        <v>-0.1256</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2627</v>
+        <v>-0.0611</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3943</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8815</v>
+        <v>-1.7292</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.5159</v>
+        <v>-3.162</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6344</v>
+        <v>1.4328</v>
       </c>
       <c r="G19" t="n">
         <v>1.6944</v>
@@ -1936,13 +1936,13 @@
         <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3233</v>
+        <v>-0.1711</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8136</v>
+        <v>-0.4597</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4903</v>
+        <v>0.2886</v>
       </c>
       <c r="V19" t="n">
         <v>-1.8608</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1371</v>
+        <v>-1.9348</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3005</v>
+        <v>-1.0646</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8365</v>
+        <v>-0.8701</v>
       </c>
       <c r="G20" t="n">
         <v>0.1302</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4116</v>
+        <v>-0.2093</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0365</v>
+        <v>0.0029</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4089</v>
+        <v>-2.7905</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9094</v>
+        <v>-3.2412</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4995</v>
+        <v>0.4507</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7477</v>
+        <v>0.6846</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0156</v>
+        <v>0.4369</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7632</v>
+        <v>0.2477</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5788</v>
+        <v>1.6281</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3948</v>
+        <v>1.163</v>
       </c>
       <c r="L21" t="n">
-        <v>0.184</v>
+        <v>0.465</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3265</v>
+        <v>-0.9434</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3792</v>
+        <v>-0.7261</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9473</v>
+        <v>-0.2173</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8556</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-4.639</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4084</v>
+        <v>-0.0138</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9911</v>
+        <v>-0.7664</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4173</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.214</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X21" t="n">
         <v>-1.214</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8083</v>
+        <v>-3.0937</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5951</v>
+        <v>-1.6171</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7868000000000001</v>
+        <v>-1.4766</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6846</v>
+        <v>-0.7477</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4369</v>
+        <v>1.0156</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477</v>
+        <v>-1.7632</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6281</v>
+        <v>1.5788</v>
       </c>
       <c r="K22" t="n">
-        <v>1.163</v>
+        <v>1.3948</v>
       </c>
       <c r="L22" t="n">
-        <v>0.465</v>
+        <v>0.184</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9434</v>
+        <v>-2.3265</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7261</v>
+        <v>-0.3792</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2173</v>
+        <v>-1.9473</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.7834</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.639</v>
+        <v>-3.4793</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0316</v>
+        <v>0.7235</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1202</v>
+        <v>0.2833</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0886</v>
+        <v>0.4402</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.214</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>-1.214</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9626</v>
+        <v>-3.5251</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4018</v>
+        <v>-3.1659</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5608</v>
+        <v>-0.3592</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0995</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1826</v>
+        <v>-0.7451</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7345</v>
+        <v>-0.5329</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1444</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. PAJOLA</t>
+          <t>C. EDWARDS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.4951</v>
+        <v>-5.8033</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.0067</v>
+        <v>-4.8701</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4884</v>
+        <v>-0.9332</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.2237</v>
+        <v>-3.7051</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1357</v>
+        <v>-0.6066</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.3594</v>
+        <v>-3.0985</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.0229</v>
+        <v>-2.1186</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3361</v>
+        <v>-0.9706</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.359</v>
+        <v>-1.148</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2008</v>
+        <v>-1.5865</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2004</v>
+        <v>0.364</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0004</v>
+        <v>-1.9505</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.7834</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4793</v>
+        <v>-2.5515</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5843</v>
+        <v>-0.3301</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4955</v>
+        <v>-0.2001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0887</v>
+        <v>-0.13</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C. EDWARDS</t>
+          <t>A. PAJOLA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.6162</v>
+        <v>-6.6409</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.9881</v>
+        <v>-5.2426</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6281</v>
+        <v>-1.3983</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.7051</v>
+        <v>-3.2237</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6066</v>
+        <v>0.1357</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.0985</v>
+        <v>-3.3594</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.1186</v>
+        <v>-2.0229</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.9706</v>
+        <v>0.3361</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.148</v>
+        <v>-2.359</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5865</v>
+        <v>-1.2008</v>
       </c>
       <c r="N25" t="n">
-        <v>0.364</v>
+        <v>-0.2004</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.9505</v>
+        <v>-1.0004</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6959</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.5515</v>
+        <v>-3.4793</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1431</v>
+        <v>0.4384</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3181</v>
+        <v>0.2596</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.825</v>
+        <v>0.1788</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-17.7137</v>
+        <v>-16.9271</v>
       </c>
       <c r="E26" t="n">
-        <v>-17.7747</v>
+        <v>-17.7746</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06109999999999993</v>
+        <v>0.847499999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-3.946099999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>3.414699999999999</v>
+        <v>3.4147</v>
       </c>
       <c r="I26" t="n">
         <v>-7.3611</v>
@@ -2458,16 +2458,16 @@
         <v>3.897099999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>3.3292</v>
+        <v>3.329199999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5678000000000007</v>
+        <v>0.567800000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-7.843</v>
       </c>
       <c r="N26" t="n">
-        <v>0.08579999999999988</v>
+        <v>0.08579999999999974</v>
       </c>
       <c r="O26" t="n">
         <v>-7.9288</v>
@@ -2482,19 +2482,19 @@
         <v>17.3966</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7467999999999998</v>
+        <v>0.03950000000000004</v>
       </c>
       <c r="T26" t="n">
         <v>-1.4718</v>
       </c>
       <c r="U26" t="n">
-        <v>0.7248000000000001</v>
+        <v>1.5112</v>
       </c>
       <c r="V26" t="n">
         <v>-7.2218</v>
       </c>
       <c r="W26" t="n">
-        <v>2.995200000000001</v>
+        <v>2.9952</v>
       </c>
       <c r="X26" t="n">
         <v>-10.217</v>
